--- a/data/raw/sales/Week 10/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 10/Audio_Array/other_channels.xlsx
@@ -4360,7 +4360,7 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>AH-60 BL</t>
+          <t>AH-60-BL</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>AH-60 RD</t>
+          <t>AH-60-RD</t>
         </is>
       </c>
       <c r="C59" s="27" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="B89" s="27" t="inlineStr">
         <is>
-          <t>AM-Mix4 OTG</t>
+          <t>BE-4T</t>
         </is>
       </c>
       <c r="C89" s="27" t="inlineStr">

--- a/data/raw/sales/Week 10/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 10/Audio_Array/other_channels.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 10\Audio_Array\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 10\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987A013B-6120-4DBB-85C5-C8A83A01F2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
